--- a/consent_forms/041_nurse_practitioner_preceptor_commitment_form--consent_forms.xlsx
+++ b/consent_forms/041_nurse_practitioner_preceptor_commitment_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Page</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rotation Information</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clinical Site Information</t>
+          <t>What is your role as a preceptor?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +594,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rotation Dates</t>
+          <t>Rotation Information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rotation Time</t>
+          <t>Clinical Site Information</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Clinical Site Information</t>
+          <t>What is the clinical site address?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rotation Dates</t>
+          <t>Clinical Site Contact</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rotation Time</t>
+          <t>Rotation Dates and Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rotation Information</t>
+          <t>What is the rotation start date?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rotation Dates</t>
+          <t>What is the rotation end date?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rotation Time</t>
+          <t>What is the rotation start time?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,20 +778,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rotation Information</t>
+          <t>What is the rotation end time?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rotation Dates</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rotation Time</t>
+          <t>Is there any additional information you would like to provide about your clinical site or rotation?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,20 +847,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rotation Information</t>
+          <t>I confirm that the information provided is accurate and complete</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -870,312 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rotation Dates</t>
+          <t>Signature of the preceptor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Rotation Time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rotation Information</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Rotation Dates</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Rotation Time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Rotation Information</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Rotation Dates</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Rotation Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Rotation Information</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Rotation End Date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>form_26</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Rotation End Time</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>form_27</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Rotation End Date</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>form_28</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Rotation End Time</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>form_29</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Clinical Site Information</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1194,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1218,51 +919,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>what_is_the_rotation_duration?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'option_1'}</t>
+          <t>What is the rotation duration?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>what_are_the_rotation_dates?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'option_2'}</t>
+          <t>What are the rotation dates?</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_2_choices</t>
+          <t>form_4_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>what_is_the_rotation_time?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'option_3'}</t>
+          <t>What is the rotation time?</t>
         </is>
       </c>
     </row>
